--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2023_arica_y_parinacota.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:49</t>
+    <t xml:space="preserve">2026-09-24 01:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -807,10 +807,10 @@
         <v>26</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>-0.72</v>
+        <v>-0.73</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="21">
@@ -821,10 +821,10 @@
         <v>26</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.27</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22">
@@ -835,10 +835,10 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.65</v>
+        <v>-0.66</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="23">
@@ -877,10 +877,10 @@
         <v>32</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.29</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="26">
@@ -891,10 +891,10 @@
         <v>32</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="27">
@@ -905,10 +905,10 @@
         <v>32</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.19</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="28">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2023_arica_y_parinacota.xlsx
@@ -117,7 +117,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:38</t>
+    <t xml:space="preserve">2026-10-01 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2023_arica_y_parinacota.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:07</t>
+    <t xml:space="preserve">2026-10-05 20:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
